--- a/S4_Boosting/Week-4/boosting_family_results.xlsx
+++ b/S4_Boosting/Week-4/boosting_family_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,42 +439,62 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>monotone_constraints</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>n_estimators</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>max_iter</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>monotonic_cst</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>MAE_CD</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>RMSE_CD</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>R_CD</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>max_depth</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>monotone_constraints</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t>n_estimators</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>max_iter</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>monotonic_cst</t>
         </is>
       </c>
     </row>
@@ -485,37 +505,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.074579046426211</v>
+        <v>3.217409360174106</v>
       </c>
       <c r="C2" t="n">
-        <v>4.681136241601092</v>
+        <v>4.714843568348019</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9183827773601871</v>
+        <v>0.9145215830764282</v>
       </c>
       <c r="E2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>(1, 0, 0, -1, 0, 0, 0, 1)</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>50</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v>3.029132828993685</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4.90691408069064</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.9228962503940124</v>
+      </c>
+      <c r="M2" t="n">
         <v>3</v>
       </c>
-      <c r="F2" t="n">
-        <v>500</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="n">
-        <v>3.029132828993685</v>
-      </c>
-      <c r="I2" t="n">
-        <v>4.90691408069064</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.9228962503940124</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3</v>
-      </c>
-      <c r="L2" t="n">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>(0, 0, 0, 0, 0, 0, 0, 0)</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
         <v>1000</v>
       </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -524,36 +556,48 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.062682783140068</v>
+        <v>3.291137907692869</v>
       </c>
       <c r="C3" t="n">
-        <v>4.419067689306043</v>
+        <v>4.97329762518588</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9272654832774805</v>
+        <v>0.904893369680253</v>
       </c>
       <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>[0, 0, 0, 0, 0, 0, 0, 0]</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>2.954145779586261</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.750469112105931</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.9277344040350028</v>
+      </c>
+      <c r="M3" t="n">
         <v>5</v>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="n">
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
         <v>1000</v>
       </c>
-      <c r="H3" t="n">
-        <v>2.954145779586261</v>
-      </c>
-      <c r="I3" t="n">
-        <v>4.750469112105931</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.9277344040350028</v>
-      </c>
-      <c r="K3" t="n">
-        <v>5</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="n">
-        <v>1000</v>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>[0, 0, 0, 0, 0, 0, 0, 0]</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -568,20 +612,24 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="n">
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="n">
         <v>6.394682086184696</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>7.694565872017636</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>0.8104050195229335</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="n">
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="n">
         <v>500</v>
       </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/S4_Boosting/Week-4/boosting_family_results.xlsx
+++ b/S4_Boosting/Week-4/boosting_family_results.xlsx
@@ -1,40 +1,87 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
+  <si>
+    <t>MAE</t>
+  </si>
+  <si>
+    <t>RMSE</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>max_depth</t>
+  </si>
+  <si>
+    <t>n_estimators</t>
+  </si>
+  <si>
+    <t>max_iter</t>
+  </si>
+  <si>
+    <t>MAE_CD</t>
+  </si>
+  <si>
+    <t>RMSE_CD</t>
+  </si>
+  <si>
+    <t>R_CD</t>
+  </si>
+  <si>
+    <t>XGBRegressor</t>
+  </si>
+  <si>
+    <t>HistGradientBoostingRegressor</t>
+  </si>
+  <si>
+    <t>AdaBoostRegressor</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,85 +89,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -408,230 +406,136 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Q4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>MAE</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>RMSE</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>max_depth</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>monotone_constraints</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>n_estimators</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>max_iter</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>monotonic_cst</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>MAE_CD</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>RMSE_CD</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>R_CD</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>max_depth</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>monotone_constraints</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>n_estimators</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>max_iter</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>monotonic_cst</t>
-        </is>
+    <row r="1" spans="1:13">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>XGBRegressor</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3.217409360174106</v>
-      </c>
-      <c r="C2" t="n">
-        <v>4.714843568348019</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.9145215830764282</v>
-      </c>
-      <c r="E2" t="n">
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2">
+        <v>3.029579782073626</v>
+      </c>
+      <c r="C2">
+        <v>4.518616399708103</v>
+      </c>
+      <c r="D2">
+        <v>0.9214885781323684</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>250</v>
+      </c>
+      <c r="H2">
+        <v>3.061706458237964</v>
+      </c>
+      <c r="I2">
+        <v>4.731199859796769</v>
+      </c>
+      <c r="J2">
+        <v>0.9283194745925449</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
+      </c>
+      <c r="L2">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>(1, 0, 0, -1, 0, 0, 0, 1)</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>50</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="n">
-        <v>3.029132828993685</v>
-      </c>
-      <c r="K2" t="n">
-        <v>4.90691408069064</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.9228962503940124</v>
-      </c>
-      <c r="M2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>(0, 0, 0, 0, 0, 0, 0, 0)</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
+      <c r="B3">
+        <v>3.141886306892482</v>
+      </c>
+      <c r="C3">
+        <v>4.840433754437349</v>
+      </c>
+      <c r="D3">
+        <v>0.9099071229851851</v>
+      </c>
+      <c r="E3">
+        <v>6</v>
+      </c>
+      <c r="G3">
+        <v>500</v>
+      </c>
+      <c r="H3">
+        <v>2.944391185745714</v>
+      </c>
+      <c r="I3">
+        <v>4.750336552668787</v>
+      </c>
+      <c r="J3">
+        <v>0.9277384370485199</v>
+      </c>
+      <c r="K3">
+        <v>6</v>
+      </c>
+      <c r="M3">
         <v>1000</v>
       </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>HistGradientBoostingRegressor</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>3.291137907692869</v>
-      </c>
-      <c r="C3" t="n">
-        <v>4.97329762518588</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.904893369680253</v>
-      </c>
-      <c r="E3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>[0, 0, 0, 0, 0, 0, 0, 0]</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>2.954145779586261</v>
-      </c>
-      <c r="K3" t="n">
-        <v>4.750469112105931</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.9277344040350028</v>
-      </c>
-      <c r="M3" t="n">
-        <v>5</v>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>[0, 0, 0, 0, 0, 0, 0, 0]</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>AdaBoostRegressor</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="n">
-        <v>6.394682086184696</v>
-      </c>
-      <c r="K4" t="n">
-        <v>7.694565872017636</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.8104050195229335</v>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="n">
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4">
+        <v>6.394624529480055</v>
+      </c>
+      <c r="I4">
+        <v>7.685702950679733</v>
+      </c>
+      <c r="J4">
+        <v>0.8108415347646114</v>
+      </c>
+      <c r="L4">
         <v>500</v>
       </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/S4_Boosting/Week-4/boosting_family_results.xlsx
+++ b/S4_Boosting/Week-4/boosting_family_results.xlsx
@@ -1,87 +1,49 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary_Ordered" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Side_by_Side_Combined" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw_Baseline" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exp_A_Baseline" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exp_B_Monotonic" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exp_C_SampleWeight" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exp_D_Mono_Weight" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
-  <si>
-    <t>MAE</t>
-  </si>
-  <si>
-    <t>RMSE</t>
-  </si>
-  <si>
-    <t>R</t>
-  </si>
-  <si>
-    <t>max_depth</t>
-  </si>
-  <si>
-    <t>n_estimators</t>
-  </si>
-  <si>
-    <t>max_iter</t>
-  </si>
-  <si>
-    <t>MAE_CD</t>
-  </si>
-  <si>
-    <t>RMSE_CD</t>
-  </si>
-  <si>
-    <t>R_CD</t>
-  </si>
-  <si>
-    <t>XGBRegressor</t>
-  </si>
-  <si>
-    <t>HistGradientBoostingRegressor</t>
-  </si>
-  <si>
-    <t>AdaBoostRegressor</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -90,18 +52,37 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -109,16 +90,83 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -406,136 +454,1315 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Experiment</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Best Parameters</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Raw Dataset Baseline</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>XGBRegressor</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>3.029579782073626</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4.518616399708103</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.9214885781323684</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>max_depth=5, n_estimators=250</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Raw Dataset Baseline</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>HistGradientBoostingRegressor</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>3.141886306892482</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.840433754437349</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.9099071229851851</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>max_depth=6, max_iter=500</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Exp A: Baseline (Cleaned)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>XGBRegressor</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3.061706458237964</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.731199859796769</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9283194745925449</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>max_depth=3, n_estimators=500</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Exp A: Baseline (Cleaned)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>HistGradientBoostingRegressor</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2.944391185745714</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.750336552668787</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9277384370485199</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>max_depth=6, max_iter=1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Exp A: Baseline (Cleaned)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>AdaBoostRegressor</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>6.394624529480055</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7.685702950679733</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.8108415347646114</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>n_estimators=500</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Exp B: Monotonic (Cleaned)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>XGBRegressor</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>3.515409990981584</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5.133643417860124</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9156063073152729</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>max_depth=6, n_estimators=50</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Exp B: Monotonic (Cleaned)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>HistGradientBoostingRegressor</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3.242481782747652</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.878659338340279</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.9237816436761246</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>max_depth=6, max_iter=1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Exp C: Sample Weight (Cleaned)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>XGBRegressor</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3.029132828993685</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.90691408069064</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9228962503940124</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>max_depth=3, n_estimators=1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Exp C: Sample Weight (Cleaned)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HistGradientBoostingRegressor</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2.954145779586261</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.750469112105931</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9277344040350028</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>max_depth=5, max_iter=1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Exp C: Sample Weight (Cleaned)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>AdaBoostRegressor</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>6.394682086184696</v>
+      </c>
+      <c r="D11" t="n">
+        <v>7.694565872017636</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.8104050195229335</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>n_estimators=500</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Exp D: Monotonic + Sample Weight (Cleaned)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>XGBRegressor</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>3.064027662846354</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4.696722380922885</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.9293603771708739</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>max_depth=10, n_estimators=50</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Exp D: Monotonic + Sample Weight (Cleaned)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>HistGradientBoostingRegressor</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3.338735172763197</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4.936675160122422</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.921958125299705</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>max_depth=6, max_iter=1000</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AE6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr"/>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Raw Baseline</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Exp A (Baseline)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Exp B (Monotonic)</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="n"/>
+      <c r="R1" s="1" t="n"/>
+      <c r="S1" s="1" t="n"/>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Exp C (Sample Weight)</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="n"/>
+      <c r="V1" s="1" t="n"/>
+      <c r="W1" s="1" t="n"/>
+      <c r="X1" s="1" t="n"/>
+      <c r="Y1" s="1" t="n"/>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Exp D (Monotonic + Weight)</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="n"/>
+      <c r="AB1" s="1" t="n"/>
+      <c r="AC1" s="1" t="n"/>
+      <c r="AD1" s="1" t="n"/>
+      <c r="AE1" s="1" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr"/>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>MAE_Raw</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_Raw</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>R2_Raw</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>max_depth</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>n_estimators</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>max_iter</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>MAE_A</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_A</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>R2_A</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>max_depth</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>n_estimators</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>max_iter</t>
+        </is>
+      </c>
+      <c r="N2" s="1" t="inlineStr">
+        <is>
+          <t>MAE_B</t>
+        </is>
+      </c>
+      <c r="O2" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_B</t>
+        </is>
+      </c>
+      <c r="P2" s="1" t="inlineStr">
+        <is>
+          <t>R2_B</t>
+        </is>
+      </c>
+      <c r="Q2" s="1" t="inlineStr">
+        <is>
+          <t>max_depth</t>
+        </is>
+      </c>
+      <c r="R2" s="1" t="inlineStr">
+        <is>
+          <t>n_estimators</t>
+        </is>
+      </c>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>max_iter</t>
+        </is>
+      </c>
+      <c r="T2" s="1" t="inlineStr">
+        <is>
+          <t>MAE_C</t>
+        </is>
+      </c>
+      <c r="U2" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_C</t>
+        </is>
+      </c>
+      <c r="V2" s="1" t="inlineStr">
+        <is>
+          <t>R2_C</t>
+        </is>
+      </c>
+      <c r="W2" s="1" t="inlineStr">
+        <is>
+          <t>max_depth</t>
+        </is>
+      </c>
+      <c r="X2" s="1" t="inlineStr">
+        <is>
+          <t>n_estimators</t>
+        </is>
+      </c>
+      <c r="Y2" s="1" t="inlineStr">
+        <is>
+          <t>max_iter</t>
+        </is>
+      </c>
+      <c r="Z2" s="1" t="inlineStr">
+        <is>
+          <t>MAE_D</t>
+        </is>
+      </c>
+      <c r="AA2" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_D</t>
+        </is>
+      </c>
+      <c r="AB2" s="1" t="inlineStr">
+        <is>
+          <t>R2_D</t>
+        </is>
+      </c>
+      <c r="AC2" s="1" t="inlineStr">
+        <is>
+          <t>max_depth</t>
+        </is>
+      </c>
+      <c r="AD2" s="1" t="inlineStr">
+        <is>
+          <t>n_estimators</t>
+        </is>
+      </c>
+      <c r="AE2" s="1" t="inlineStr">
+        <is>
+          <t>max_iter</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>XGBRegressor</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.029579782073626</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4.518616399708103</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.9214885781323684</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>250</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>3.061706458237964</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.731199859796769</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.9283194745925449</v>
+      </c>
+      <c r="K4" t="n">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="L4" t="n">
+        <v>500</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>3.515409990981584</v>
+      </c>
+      <c r="O4" t="n">
+        <v>5.133643417860124</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.9156063073152729</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>6</v>
+      </c>
+      <c r="R4" t="n">
+        <v>50</v>
+      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="n">
+        <v>3.029132828993685</v>
+      </c>
+      <c r="U4" t="n">
+        <v>4.90691408069064</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.9228962503940124</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="n">
+        <v>3.064027662846354</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>4.696722380922885</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9293603771708739</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AE4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>HistGradientBoostingRegressor</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.141886306892482</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4.840433754437349</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.9099071229851851</v>
+      </c>
+      <c r="E5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>500</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.944391185745714</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.750336552668787</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.9277384370485199</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3.242481782747652</v>
+      </c>
+      <c r="O5" t="n">
+        <v>4.878659338340279</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.9237816436761246</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>6</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.954145779586261</v>
+      </c>
+      <c r="U5" t="n">
+        <v>4.750469112105931</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.9277344040350028</v>
+      </c>
+      <c r="W5" t="n">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.338735172763197</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>4.936675160122422</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.921958125299705</v>
+      </c>
+      <c r="AC5" t="n">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>AdaBoostRegressor</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>6.394624529480055</v>
+      </c>
+      <c r="I6" t="n">
+        <v>7.685702950679733</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.8108415347646114</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>500</v>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>6.394682086184696</v>
+      </c>
+      <c r="U6" t="n">
+        <v>7.694565872017636</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.8104050195229335</v>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="n">
+        <v>500</v>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="Z1:AE1"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="T1:Y1"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>MAE_Raw</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_Raw</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>R2_Raw</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>max_depth</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>n_estimators</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>max_iter</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>XGBRegressor</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.029579782073626</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4.518616399708103</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.9214885781323684</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>250</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>HistGradientBoostingRegressor</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.141886306892482</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4.840433754437349</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.9099071229851851</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>500</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>MAE_A</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_A</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>R2_A</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>max_depth</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>n_estimators</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>max_iter</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>XGBRegressor</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.061706458237964</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4.731199859796769</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.9283194745925449</v>
+      </c>
+      <c r="E2" t="n">
         <v>3</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="M1" s="1" t="s">
+      <c r="F2" t="n">
+        <v>500</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>HistGradientBoostingRegressor</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.944391185745714</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4.750336552668787</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.9277384370485199</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>AdaBoostRegressor</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>6.394624529480055</v>
+      </c>
+      <c r="C4" t="n">
+        <v>7.685702950679733</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.8108415347646114</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>500</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>MAE_B</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_B</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>R2_B</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>max_depth</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>n_estimators</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>max_iter</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>XGBRegressor</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.515409990981584</v>
+      </c>
+      <c r="C2" t="n">
+        <v>5.133643417860124</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.9156063073152729</v>
+      </c>
+      <c r="E2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>HistGradientBoostingRegressor</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.242481782747652</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4.878659338340279</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.9237816436761246</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>MAE_C</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_C</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>R2_C</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>max_depth</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>n_estimators</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>max_iter</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>XGBRegressor</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.029132828993685</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4.90691408069064</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.9228962503940124</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>HistGradientBoostingRegressor</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.954145779586261</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4.750469112105931</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.9277344040350028</v>
+      </c>
+      <c r="E3" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2">
-        <v>3.029579782073626</v>
-      </c>
-      <c r="C2">
-        <v>4.518616399708103</v>
-      </c>
-      <c r="D2">
-        <v>0.9214885781323684</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
-      <c r="F2">
-        <v>250</v>
-      </c>
-      <c r="H2">
-        <v>3.061706458237964</v>
-      </c>
-      <c r="I2">
-        <v>4.731199859796769</v>
-      </c>
-      <c r="J2">
-        <v>0.9283194745925449</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="L2">
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>AdaBoostRegressor</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>6.394682086184696</v>
+      </c>
+      <c r="C4" t="n">
+        <v>7.694565872017636</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.8104050195229335</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
         <v>500</v>
       </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
+      <c r="G4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>MAE_D</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_D</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>R2_D</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>max_depth</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>n_estimators</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>max_iter</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>XGBRegressor</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.064027662846354</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4.696722380922885</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.9293603771708739</v>
+      </c>
+      <c r="E2" t="n">
         <v>10</v>
       </c>
-      <c r="B3">
-        <v>3.141886306892482</v>
-      </c>
-      <c r="C3">
-        <v>4.840433754437349</v>
-      </c>
-      <c r="D3">
-        <v>0.9099071229851851</v>
-      </c>
-      <c r="E3">
+      <c r="F2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>HistGradientBoostingRegressor</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.338735172763197</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4.936675160122422</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.921958125299705</v>
+      </c>
+      <c r="E3" t="n">
         <v>6</v>
       </c>
-      <c r="G3">
-        <v>500</v>
-      </c>
-      <c r="H3">
-        <v>2.944391185745714</v>
-      </c>
-      <c r="I3">
-        <v>4.750336552668787</v>
-      </c>
-      <c r="J3">
-        <v>0.9277384370485199</v>
-      </c>
-      <c r="K3">
-        <v>6</v>
-      </c>
-      <c r="M3">
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="n">
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4">
-        <v>6.394624529480055</v>
-      </c>
-      <c r="I4">
-        <v>7.685702950679733</v>
-      </c>
-      <c r="J4">
-        <v>0.8108415347646114</v>
-      </c>
-      <c r="L4">
-        <v>500</v>
-      </c>
-    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>